--- a/manuscript/tables/e-table-3-medications.xlsx
+++ b/manuscript/tables/e-table-3-medications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/newer-glp1-dementia-repkit/manuscript/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gwenaubrac/Desktop/Gwen's Documents/Work/Boston University GRA/Projects/GLP1s for AD/03_analysis/newer-glp1-dementia-repkit/manuscript/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F050A6B-F143-0846-8E94-3B2A5745ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B3B4D7-1060-3D4A-B3DA-93C004107F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{609CF3B9-5A65-3C45-8EA5-C785028ABE13}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>Tirzepatide</t>
   </si>
   <si>
-    <t>Primary exposure (GLP-1 agonists)</t>
-  </si>
-  <si>
     <t>Rybelsus, Ozempic, Wegovy</t>
   </si>
   <si>
@@ -267,6 +264,9 @@
   </si>
   <si>
     <t>Inpefa</t>
+  </si>
+  <si>
+    <t>Primary exposure (GLP-1 RAs)</t>
   </si>
 </sst>
 </file>
@@ -341,10 +341,6 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -405,6 +401,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -438,12 +438,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52AD553B-66EC-774F-AD1D-83DF5355B527}" name="Table2" displayName="Table2" ref="A1:C41" totalsRowShown="0" headerRowDxfId="4" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52AD553B-66EC-774F-AD1D-83DF5355B527}" name="Table2" displayName="Table2" ref="A1:C41" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:C41" xr:uid="{52AD553B-66EC-774F-AD1D-83DF5355B527}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{16940BBC-AFB3-3343-A6A2-E5959C735CD4}" name="Group" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{59D51277-A055-3945-ADFC-602DACCAA329}" name="Generic Name" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{6C782C48-150F-A545-9CDB-54150B06CD2C}" name="Drug Names" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{16940BBC-AFB3-3343-A6A2-E5959C735CD4}" name="Group" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{59D51277-A055-3945-ADFC-602DACCAA329}" name="Generic Name" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{6C782C48-150F-A545-9CDB-54150B06CD2C}" name="Drug Names" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -780,15 +780,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -798,7 +798,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -806,12 +806,12 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -825,82 +825,82 @@
     </row>
     <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -912,193 +912,193 @@
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
     </row>
     <row r="33" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B35" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B36" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B38" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B39" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B40" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="34" x14ac:dyDescent="0.2">
       <c r="B41" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
